--- a/artfynd/A 48706-2023 artfynd.xlsx
+++ b/artfynd/A 48706-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48706-2023 artfynd.xlsx
+++ b/artfynd/A 48706-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>76196779</v>
+        <v>103120831</v>
       </c>
       <c r="B2" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>4368</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lomtjärn N om, Dlr</t>
+          <t>St.Lomtjärn V om, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523187.0378991614</v>
+        <v>522957</v>
       </c>
       <c r="R2" t="n">
-        <v>6691902.778716453</v>
+        <v>6691801</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,27 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Granlåga (dubbel(betesskadad), dog stående).</t>
+          <t>2022-08-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,62 +784,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>76196736</v>
+        <v>112846494</v>
       </c>
       <c r="B3" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lomtjärn NV om, Dlr</t>
+          <t>St.Lomtjärn V om, St.Lomtjärn V om, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523051.8078642784</v>
+        <v>522938</v>
       </c>
       <c r="R3" t="n">
-        <v>6691814.840280392</v>
+        <v>6691832</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,27 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2023-10-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2023-10-21</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Torrgran 7 cm, 7 m.</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,22 +897,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103120831</v>
+        <v>112878101</v>
       </c>
       <c r="B4" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,26 +915,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4368</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -976,14 +946,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>St.Lomtjärn V om, Dlr</t>
+          <t>St. Lomtjärn O om, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522957.7314026441</v>
+        <v>523367</v>
       </c>
       <c r="R4" t="n">
-        <v>6691801.38108302</v>
+        <v>6691843</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,22 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-08-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-08-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,72 +1006,64 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112846494</v>
+        <v>76196736</v>
       </c>
       <c r="B5" t="n">
-        <v>97171</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>St.Lomtjärn V om (St.Lomtjärn V om), Dlr</t>
+          <t>Lomtjärn NV om, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522937</v>
+        <v>523052</v>
       </c>
       <c r="R5" t="n">
-        <v>6691832</v>
+        <v>6691815</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1135,22 +1087,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-10-21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-10-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2018-07-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Torrgran 7 cm, 7 m.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,22 +1118,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens, Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112878101</v>
+        <v>76196779</v>
       </c>
       <c r="B6" t="n">
-        <v>91205</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,45 +1136,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>St. Lomtjärn O om, Dlr</t>
+          <t>Lomtjärn N om, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523367</v>
+        <v>523187</v>
       </c>
       <c r="R6" t="n">
-        <v>6691843</v>
+        <v>6691903</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,12 +1199,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-10-21</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-10-21</t>
+          <t>2018-07-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Granlåga (dubbel(betesskadad), dog stående).</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,10 +1230,351 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>112850021</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ormpussen V om, Ormpussen V om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>523346</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6691979</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-10-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-10-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
           <t>Bo karlstens, Kajsa Larsson</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118747535</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>St.Lomtjärn, St.Lomtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>523285</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6691781</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>60358241</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ormpussen SV. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>523441</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6691994</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2016-06-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2016-06-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I basen på ca)15 m stup som vetter mot öster.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48706-2023 artfynd.xlsx
+++ b/artfynd/A 48706-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>76196736</v>
+        <v>135434712</v>
       </c>
       <c r="B4" t="n">
-        <v>5179</v>
+        <v>4776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,46 +904,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lomtjärn NV om, Dlr</t>
+          <t>Dammsjön/Gethällsklack, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523052</v>
+        <v>523412</v>
       </c>
       <c r="R4" t="n">
-        <v>6691815</v>
+        <v>6691981</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,17 +963,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Torrgran 7 cm, 7 m.</t>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,7 +1006,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>76196779</v>
+        <v>76196736</v>
       </c>
       <c r="B5" t="n">
         <v>5179</v>
@@ -1045,14 +1046,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lomtjärn N om, Dlr</t>
+          <t>Lomtjärn NV om, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523187</v>
+        <v>523052</v>
       </c>
       <c r="R5" t="n">
-        <v>6691903</v>
+        <v>6691815</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1090,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Granlåga (dubbel(betesskadad), dog stående).</t>
+          <t>Torrgran 7 cm, 7 m.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,60 +1118,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112846494</v>
+        <v>76196779</v>
       </c>
       <c r="B6" t="n">
-        <v>99118</v>
+        <v>5179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>St.Lomtjärn V om, St.Lomtjärn V om, Dlr</t>
+          <t>Lomtjärn N om, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522938</v>
+        <v>523187</v>
       </c>
       <c r="R6" t="n">
-        <v>6691832</v>
+        <v>6691903</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,22 +1192,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-10-21</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-10-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2018-07-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Granlåga (dubbel(betesskadad), dog stående).</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,67 +1223,60 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens, Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112850021</v>
+        <v>135434711</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>5181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ormpussen V om, Ormpussen V om, Dlr</t>
+          <t>Dammsjön/Gethällsklack, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523346</v>
+        <v>523412</v>
       </c>
       <c r="R7" t="n">
-        <v>6691979</v>
+        <v>6691981</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,22 +1300,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-10-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-10-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,7 +1324,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1350,14 +1335,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens, Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118747535</v>
+        <v>112846494</v>
       </c>
       <c r="B8" t="n">
         <v>99118</v>
@@ -1387,27 +1372,30 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>St.Lomtjärn, St.Lomtjärn, Dlr</t>
+          <t>St.Lomtjärn V om, St.Lomtjärn V om, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523285</v>
+        <v>522938</v>
       </c>
       <c r="R8" t="n">
-        <v>6691781</v>
+        <v>6691832</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1431,22 +1419,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2023-10-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2023-10-21</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,6 +1443,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1466,58 +1455,67 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>60358241</v>
+        <v>112850021</v>
       </c>
       <c r="B9" t="n">
-        <v>101326</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ormpussen SV. om, Dlr</t>
+          <t>Ormpussen V om, Ormpussen V om, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523441</v>
+        <v>523346</v>
       </c>
       <c r="R9" t="n">
-        <v>6691994</v>
+        <v>6691979</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1541,17 +1539,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2016-06-12</t>
+          <t>2023-10-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2016-06-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>I basen på ca)15 m stup som vetter mot öster.</t>
+          <t>2023-10-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,6 +1563,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1571,10 +1575,231 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
+          <t>Bo karlstens, Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118747535</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>St.Lomtjärn, St.Lomtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>523285</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6691781</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Bo karlstens</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>60358241</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ormpussen SV. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>523441</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6691994</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2016-06-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2016-06-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>I basen på ca)15 m stup som vetter mot öster.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48706-2023 artfynd.xlsx
+++ b/artfynd/A 48706-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112878101</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103120831</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135434712</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76196736</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76196779</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1339,6 +1369,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135434711</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1459,6 +1494,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112846494</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1579,6 +1619,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112850021</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1695,6 +1740,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118747535</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1800,8 +1850,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60358241</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 48706-2023 artfynd.xlsx
+++ b/artfynd/A 48706-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>76196736</v>
+        <v>135434712</v>
       </c>
       <c r="B4" t="n">
-        <v>5179</v>
+        <v>4776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,46 +919,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lomtjärn NV om, Dlr</t>
+          <t>Dammsjön/Gethällsklack, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523052</v>
+        <v>523412</v>
       </c>
       <c r="R4" t="n">
-        <v>6691815</v>
+        <v>6691981</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,17 +978,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-07-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Torrgran 7 cm, 7 m.</t>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,13 +1020,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/76196736</t>
+          <t>https://artportalen.se/Sighting/135434712</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>76196779</v>
+        <v>76196736</v>
       </c>
       <c r="B5" t="n">
         <v>5179</v>
@@ -1065,14 +1066,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lomtjärn N om, Dlr</t>
+          <t>Lomtjärn NV om, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523187</v>
+        <v>523052</v>
       </c>
       <c r="R5" t="n">
-        <v>6691903</v>
+        <v>6691815</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1110,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Granlåga (dubbel(betesskadad), dog stående).</t>
+          <t>Torrgran 7 cm, 7 m.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,66 +1137,63 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/76196779</t>
+          <t>https://artportalen.se/Sighting/76196736</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112846494</v>
+        <v>76196779</v>
       </c>
       <c r="B6" t="n">
-        <v>99118</v>
+        <v>5179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>St.Lomtjärn V om, St.Lomtjärn V om, Dlr</t>
+          <t>Lomtjärn N om, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522938</v>
+        <v>523187</v>
       </c>
       <c r="R6" t="n">
-        <v>6691832</v>
+        <v>6691903</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,22 +1217,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-10-21</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-10-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2018-07-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Granlåga (dubbel(betesskadad), dog stående).</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,72 +1248,65 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens, Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112846494</t>
+          <t>https://artportalen.se/Sighting/76196779</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112850021</v>
+        <v>135434711</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>5181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ormpussen V om, Ormpussen V om, Dlr</t>
+          <t>Dammsjön/Gethällsklack, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523346</v>
+        <v>523412</v>
       </c>
       <c r="R7" t="n">
-        <v>6691979</v>
+        <v>6691981</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,22 +1330,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-10-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-10-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,7 +1354,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1380,19 +1365,19 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens, Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112850021</t>
+          <t>https://artportalen.se/Sighting/135434711</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118747535</v>
+        <v>112846494</v>
       </c>
       <c r="B8" t="n">
         <v>99118</v>
@@ -1422,27 +1407,30 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>St.Lomtjärn, St.Lomtjärn, Dlr</t>
+          <t>St.Lomtjärn V om, St.Lomtjärn V om, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523285</v>
+        <v>522938</v>
       </c>
       <c r="R8" t="n">
-        <v>6691781</v>
+        <v>6691832</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1466,22 +1454,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2023-10-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2023-10-21</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,6 +1478,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1501,63 +1490,72 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118747535</t>
+          <t>https://artportalen.se/Sighting/112846494</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>60358241</v>
+        <v>112850021</v>
       </c>
       <c r="B9" t="n">
-        <v>101326</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ormpussen SV. om, Dlr</t>
+          <t>Ormpussen V om, Ormpussen V om, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523441</v>
+        <v>523346</v>
       </c>
       <c r="R9" t="n">
-        <v>6691994</v>
+        <v>6691979</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1581,17 +1579,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2016-06-12</t>
+          <t>2023-10-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2016-06-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>I basen på ca)15 m stup som vetter mot öster.</t>
+          <t>2023-10-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,6 +1603,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1611,11 +1615,242 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bo karlstens, Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112850021</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118747535</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>St.Lomtjärn, St.Lomtjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>523285</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6691781</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118747535</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>60358241</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ormpussen SV. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>523441</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6691994</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2016-06-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2016-06-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>I basen på ca)15 m stup som vetter mot öster.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/60358241</t>
         </is>
@@ -1631,6 +1866,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48706-2023 artfynd.xlsx
+++ b/artfynd/A 48706-2023 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>135434712</v>
       </c>
       <c r="B4" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135434711</v>
       </c>
       <c r="B7" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
